--- a/content/KPIM/02_campaigns/CMP-2026-Q4/CMP-2026-Q4.xlsx
+++ b/content/KPIM/02_campaigns/CMP-2026-Q4/CMP-2026-Q4.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -534,20 +534,24 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Tên cột</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Là TEXT THUẦN, không có icon — trùng khớp tuyệt đối với tên trong schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>LUẬT VÀNG</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Ô nền VÀNG ở hàng tiêu đề là cột của bạn — agent không bao giờ ghi đè.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ô nền XANH LÁ do script sinh — sửa tay sẽ bị ghi đè lần chạy sau.</t>
+          <t>Nền VÀNG ở hàng tiêu đề = CỦA BẠN — agent không bao giờ ghi đè.</t>
         </is>
       </c>
     </row>
@@ -555,23 +559,23 @@
       <c r="A7" s="1" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ô nền XANH DƯƠNG do agent sinh — bạn sửa thoải mái.</t>
+          <t>Nền XANH LÁ = script sinh, sửa tay sẽ bị ghi đè.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Nền XANH DƯƠNG = agent sinh, bạn sửa thoải mái.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Ô rỗng nghĩa là gì</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ô rỗng nghĩa là CHƯA BIẾT. Không điền 0, không điền "N/A", không đoán. Riêng baseline_median rỗng = chưa đủ mẫu, dashboard phải hiện "chưa đủ mẫu".</t>
+          <t>Không nhớ màu? Mở sheet _Dictionary, cột 'ai ghi'.</t>
         </is>
       </c>
     </row>
@@ -582,140 +586,156 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>Ô rỗng nghĩa là gì</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ô rỗng nghĩa là CHƯA BIẾT. Không điền 0, không điền "N/A", không đoán. Riêng baseline_median rỗng = chưa đủ mẫu, dashboard phải hiện "chưa đủ mẫu".</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>01_Brief</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 trường của brief — Thay cho brief.yml. Brief là thứ BẠN duyệt nên phải nằm trong workbook, không nằm ở file cấu hình máy đọc.
 </t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>02_KPI_Target</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = campaign × kênh × pillar × chỉ số × kỳ — baseline_n &lt; 10 thì mọi so-sánh-với-median phải bị chặn. Đây là chỗ duy nhất giữ con số baseline — không được nhân bản sang sheet khác.
 </t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>03_Calendar</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>1 dòng = 1 asset — Sheet trung tâm. Nhìn hết một chiến dịch trên một màn hình.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>04_Content</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 asset × 1 mảnh nội dung × 1 biến thể — Tách khỏi Calendar vì một asset có nhiều mảnh nội dung (title A/B, 3 caption, prompt media) và vì text dài làm dòng Calendar cao vài trăm pixel.
 </t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>05_Approval</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 asset × 1 vòng duyệt — Tách khỏi Calendar vì một asset duyệt nhiều vòng. Gộp một dòng là mất lịch sử revise — thứ đắt nhất khi rà lại sau chiến dịch.
 </t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>06_Publish_Log</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>1 dòng = 1 asset × 1 kênh × 1 lần chạy — Vết của mọi lần publish, kể cả dry-run và lần lỗi.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>07_Metrics_Daily</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = asset × kênh × ngày — Bản nạp lại của RIÊNG chiến dịch này (≈1.700 dòng cho 31 asset × 2 kênh × 28 ngày) để soi được ngay trong file. Nguồn sự thật vẫn là CSV ở data/&lt;instance&gt;/raw|star.
 </t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>08_Metrics_Summary</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>1 dòng = asset × kênh — Chỗ trả lời câu "bài nào thắng, vì sao".</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>09_Leads</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>1 dòng = 1 lead — Bỏ sheet này nếu chiến dịch không có mục tiêu lead.</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>08_Metrics_Summary</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1 dòng = asset × kênh — Chỗ trả lời câu "bài nào thắng, vì sao".</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>09_Leads</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1 dòng = 1 lead — Bỏ sheet này nếu chiến dịch không có mục tiêu lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>10_Insights</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 phát hiện — Ép insight phải có bằng chứng. Không có evidence_metric + evidence_value thì không được ghi dòng — đây là chỗ AI hay bịa nhất.
 </t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Làm mới workbook</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>python scripts/workbook/build_workbook.py --campaign-id &lt;ID&gt; --out &lt;file&gt;</t>
         </is>
@@ -756,82 +776,82 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_id</t>
+          <t>lead_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source_raw</t>
+          <t>source_raw</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ created_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ campaign_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ pillar_code</t>
+          <t>pillar_code</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ need_type</t>
+          <t>need_type</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ product_interest</t>
+          <t>product_interest</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ region</t>
+          <t>region</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ branch</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_status</t>
+          <t>lead_status</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ priority_score</t>
+          <t>priority_score</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_segment</t>
+          <t>lead_segment</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ next_action</t>
+          <t>next_action</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ is_duplicate_of</t>
+          <t>is_duplicate_of</t>
         </is>
       </c>
     </row>
@@ -877,72 +897,72 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 insight_id</t>
+          <t>insight_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 scope</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 scope_ref</t>
+          <t>scope_ref</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 observed_at</t>
+          <t>observed_at</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 symptom</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>🤖 evidence_metric</t>
+          <t>evidence_metric</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 evidence_value</t>
+          <t>evidence_value</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_value</t>
+          <t>baseline_value</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 likely_cause</t>
+          <t>likely_cause</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 impact</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recommendation</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>🤖 priority</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_by</t>
+          <t>approved_by</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>👤 status</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6899,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6917,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6939,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6957,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6971,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6989,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6987,7 +7007,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7021,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7037,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7033,7 +7053,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7071,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7063,13 +7083,13 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Số mở tài khoản lương</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7081,13 +7101,13 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Chi phí trên mỗi lead (CPL)</t>
+          <t>cta_rate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7121,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7135,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7149,7 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7163,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7183,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7197,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7191,7 +7211,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7225,7 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7239,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7257,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>🤖 agent</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7275,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -7288,52 +7308,52 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_code</t>
+          <t>pillar_code</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 metric_name</t>
+          <t>metric_name</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 period</t>
+          <t>period</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>👤 target_value</t>
+          <t>target_value</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>👤 unit</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_median</t>
+          <t>baseline_median</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_source</t>
+          <t>baseline_source</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_n</t>
+          <t>baseline_n</t>
         </is>
       </c>
     </row>
@@ -8887,212 +8907,212 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 campaign_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 series_id</t>
+          <t>series_id</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 episode_no</t>
+          <t>episode_no</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 week_no</t>
+          <t>week_no</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>🤖 parent_asset_id</t>
+          <t>parent_asset_id</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 doc_ref</t>
+          <t>doc_ref</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_primary</t>
+          <t>pillar_primary</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_secondary</t>
+          <t>pillar_secondary</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 persona_target</t>
+          <t>persona_target</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>🤖 format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>🤖 platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>🤖 distribution_platforms</t>
+          <t>distribution_platforms</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>🤖 funnel_stage</t>
+          <t>funnel_stage</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
         <is>
-          <t>🤖 function_role</t>
+          <t>function_role</t>
         </is>
       </c>
       <c r="P1" s="8" t="inlineStr">
         <is>
-          <t>🤖 title_draft</t>
+          <t>title_draft</t>
         </is>
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>🤖 title_final</t>
+          <t>title_final</t>
         </is>
       </c>
       <c r="R1" s="8" t="inlineStr">
         <is>
-          <t>🤖 cta_type</t>
+          <t>cta_type</t>
         </is>
       </c>
       <c r="S1" s="8" t="inlineStr">
         <is>
-          <t>🤖 has_commercial_cta</t>
+          <t>has_commercial_cta</t>
         </is>
       </c>
       <c r="T1" s="8" t="inlineStr">
         <is>
-          <t>🤖 hashtags</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="U1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ hashtag_count</t>
+          <t>hashtag_count</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>🤖 planned_publish_date</t>
+          <t>planned_publish_date</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>🤖 planned_publish_time</t>
+          <t>planned_publish_time</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
         <is>
-          <t>🤖 timezone</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="Y1" s="9" t="inlineStr">
         <is>
-          <t>👤 tos_score</t>
+          <t>tos_score</t>
         </is>
       </c>
       <c r="Z1" s="9" t="inlineStr">
         <is>
-          <t>👤 hrs_score</t>
+          <t>hrs_score</t>
         </is>
       </c>
       <c r="AA1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_topic</t>
+          <t>approve_topic</t>
         </is>
       </c>
       <c r="AB1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_content</t>
+          <t>approve_content</t>
         </is>
       </c>
       <c r="AC1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_final</t>
+          <t>approve_final</t>
         </is>
       </c>
       <c r="AD1" s="8" t="inlineStr">
         <is>
-          <t>🤖 status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="AE1" s="8" t="inlineStr">
         <is>
-          <t>🤖 owner</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="AF1" s="8" t="inlineStr">
         <is>
-          <t>🤖 verification_open</t>
+          <t>verification_open</t>
         </is>
       </c>
       <c r="AG1" s="9" t="inlineStr">
         <is>
-          <t>👤 qa_passed</t>
+          <t>qa_passed</t>
         </is>
       </c>
       <c r="AH1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_by</t>
+          <t>approved_by</t>
         </is>
       </c>
       <c r="AI1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_at</t>
+          <t>approved_at</t>
         </is>
       </c>
       <c r="AJ1" s="8" t="inlineStr">
         <is>
-          <t>🤖 blocked_reason</t>
+          <t>blocked_reason</t>
         </is>
       </c>
       <c r="AK1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ actual_publish_datetime</t>
+          <t>actual_publish_datetime</t>
         </is>
       </c>
       <c r="AL1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform_native_id</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="AM1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ live_url</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="AN1" s="8" t="inlineStr">
         <is>
-          <t>🤖 playlist_id</t>
+          <t>playlist_id</t>
         </is>
       </c>
       <c r="AO1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recycle_source_id</t>
+          <t>recycle_source_id</t>
         </is>
       </c>
       <c r="AP1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recycle_due_date</t>
+          <t>recycle_due_date</t>
         </is>
       </c>
     </row>
@@ -11363,62 +11383,62 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 content_id</t>
+          <t>content_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 content_type</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 variant</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 body</t>
+          <t>body</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ char_count</t>
+          <t>char_count</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 hashtags</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>🤖 language</t>
+          <t>language</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 draft_path</t>
+          <t>draft_path</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 ai_generated</t>
+          <t>ai_generated</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ generated_at</t>
+          <t>generated_at</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>👤 is_selected</t>
+          <t>is_selected</t>
         </is>
       </c>
     </row>
@@ -11474,92 +11494,92 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>👤 review_id</t>
+          <t>review_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>👤 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>👤 round_no</t>
+          <t>round_no</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 submitted_at</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>👤 reviewer</t>
+          <t>reviewer</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>👤 decided_at</t>
+          <t>decided_at</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>👤 comment</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_primary_source</t>
+          <t>chk_primary_source</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_fact_opinion</t>
+          <t>chk_fact_opinion</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_title_no_overclaim</t>
+          <t>chk_title_no_overclaim</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_thumbnail_honest</t>
+          <t>chk_thumbnail_honest</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_subscribe_reason</t>
+          <t>chk_subscribe_reason</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_next_bridge</t>
+          <t>chk_next_bridge</t>
         </is>
       </c>
       <c r="O1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_hashtag_ok</t>
+          <t>chk_hashtag_ok</t>
         </is>
       </c>
       <c r="P1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_cta_ok</t>
+          <t>chk_cta_ok</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_no_internal_tool</t>
+          <t>chk_no_internal_tool</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_no_pii</t>
+          <t>chk_no_pii</t>
         </is>
       </c>
     </row>
@@ -11630,62 +11650,62 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ run_id</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ attempt_no</t>
+          <t>attempt_no</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ mode</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ autonomy_at_run</t>
+          <t>autonomy_at_run</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ requested_at</t>
+          <t>requested_at</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ scheduled_for</t>
+          <t>scheduled_for</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform_native_id</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ live_url</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ error_message</t>
+          <t>error_message</t>
         </is>
       </c>
     </row>
@@ -11750,137 +11770,137 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ date</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source</t>
+          <t>source</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ impressions</t>
+          <t>impressions</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ ctr</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach_organic</t>
+          <t>reach_organic</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach_paid</t>
+          <t>reach_paid</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ views</t>
+          <t>views</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engaged_views</t>
+          <t>engaged_views</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ avg_view_duration_sec</t>
+          <t>avg_view_duration_sec</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ avg_percentage_viewed</t>
+          <t>avg_percentage_viewed</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ watch_time_min</t>
+          <t>watch_time_min</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ retention_30s</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ likes</t>
+          <t>likes</t>
         </is>
       </c>
       <c r="Q1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ comments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="R1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ shares</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="S1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engagement_total</t>
+          <t>engagement_total</t>
         </is>
       </c>
       <c r="T1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ poll_votes</t>
+          <t>poll_votes</t>
         </is>
       </c>
       <c r="U1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ subscribers_gained</t>
+          <t>subscribers_gained</t>
         </is>
       </c>
       <c r="V1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ related_video_clicks</t>
+          <t>related_video_clicks</t>
         </is>
       </c>
       <c r="W1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ returning_viewers</t>
+          <t>returning_viewers</t>
         </is>
       </c>
       <c r="X1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ clicks_total</t>
+          <t>clicks_total</t>
         </is>
       </c>
       <c r="Y1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cta_clicks</t>
+          <t>cta_clicks</t>
         </is>
       </c>
       <c r="Z1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ leads</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="AA1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cost</t>
+          <t>cost</t>
         </is>
       </c>
     </row>
@@ -11930,92 +11950,92 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m24h_views</t>
+          <t>m24h_views</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m72h_views</t>
+          <t>m72h_views</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m7d_views</t>
+          <t>m7d_views</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m28d_views</t>
+          <t>m28d_views</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engagement_rate</t>
+          <t>engagement_rate</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ ctr</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cta_rate</t>
+          <t>cta_rate</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ subs_per_1000_engaged</t>
+          <t>subs_per_1000_engaged</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ retention_30s</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ vs_median_primary</t>
+          <t>vs_median_primary</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ vs_median_secondary</t>
+          <t>vs_median_secondary</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ kpi_hit_count</t>
+          <t>kpi_hit_count</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ guardrail_ok</t>
+          <t>guardrail_ok</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ is_winner</t>
+          <t>is_winner</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision_28d</t>
+          <t>decision_28d</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision_note</t>
+          <t>decision_note</t>
         </is>
       </c>
     </row>
